--- a/output/table1_descriptive.xlsx
+++ b/output/table1_descriptive.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Age (years)</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Resting BP (mm Hg)</t>
+          <t>Trestbps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serum cholesterol (mg/dl)</t>
+          <t>Chol</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maximum heart rate</t>
+          <t>Thalach</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ST depression</t>
+          <t>Oldpeak</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Number of major vessels</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fasting blood sugar &gt;120 mg/dl</t>
+          <t>Fasting blood sugar &gt;120</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Resting ECG results</t>
+          <t>Resting ECG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
